--- a/02_DIA_inicio_2026_analisis_assets/rbd_9710_escuela-basica-santa-adriana_nt2_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9710_escuela-basica-santa-adriana_nt2_nucleos.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0BA09A97-1A9A-4383-8424-CA96EDECD307}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8DA736FF-347D-415B-AB90-C7A105ACA6F1}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B99277BC-BCE3-4E88-A976-B82E5CE534A5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9682F50B-B32A-4464-ACEA-A072339EDAE2}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A4CCEF-B65C-41B4-8923-14163CD0ED1F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15F2EE5B-1793-4836-87AD-6DE3858F4B12}"/>
 </file>